--- a/docs/final/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/final/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -13455,6 +13455,17 @@
         <x:v>Implemented 2026-07-23; updated 2026-08-24 so chapter mini-wizard ready also starts the shared Master Vine VUK route chase. The chase stops as soon as the VUK starts the wizard intro. Final Showdown ready is excluded because it starts from a saucer, not the VUK.</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="85" t="str">
+        <x:v>Villain start award</x:v>
+      </x:c>
+      <x:c r="B11" s="85" t="str">
+        <x:v>100,000 + 50,000 per collected Case File</x:v>
+      </x:c>
+      <x:c r="C11" s="85" t="str">
+        <x:v>Once per gameplay attempt. Included in mode points and summary. Wizards unchanged. Machine test pending.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
